--- a/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/PivotSubtotalsSource/output.xlsx
+++ b/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/PivotSubtotalsSource/output.xlsx
@@ -78,413 +78,438 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac x16r2 xr">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="164" formatCode="mm/dd/yy"/>
-  </x:numFmts>
-  <x:fonts count="6" x14ac:knownFonts="1">
-    <x:font>
-      <x:sz val="8"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-      <x:charset val="204"/>
-    </x:font>
-    <x:font>
-      <x:sz val="8"/>
-      <x:color indexed="23"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:sz val="8"/>
-      <x:color theme="1"/>
-      <x:name val="Tahoma"/>
-      <x:family val="2"/>
-      <x:charset val="204"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-      <x:charset val="204"/>
-    </x:font>
-    <x:font>
-      <x:i/>
-      <x:sz val="8"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-      <x:charset val="204"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="11"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="2">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-  </x:fills>
-  <x:borders count="16">
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color indexed="64"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color indexed="64"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color indexed="64"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color indexed="64"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color indexed="65"/>
-      </x:left>
-      <x:right/>
-      <x:top style="thin">
-        <x:color indexed="65"/>
-      </x:top>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:left>
-      <x:right/>
-      <x:top style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:top>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color indexed="65"/>
-      </x:left>
-      <x:right/>
-      <x:top style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:top>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color indexed="65"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:top>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:left>
-      <x:right/>
-      <x:top style="thin">
-        <x:color indexed="65"/>
-      </x:top>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:top>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:top>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color indexed="65"/>
-      </x:top>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:left>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:right>
-      <x:top/>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:left>
-      <x:right/>
-      <x:top style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color indexed="65"/>
-      </x:left>
-      <x:right/>
-      <x:top style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFABABAB"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="8">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-  </x:cellStyleXfs>
-  <x:cellXfs count="43">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" pivotButton="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" pivotButton="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="2">
-    <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <x:cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-  </x:cellStyles>
-  <x:dxfs count="3">
-    <x:dxf>
-      <x:font>
-        <x:color indexed="48"/>
-      </x:font>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:sz val="10"/>
-      </x:font>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:i/>
-      </x:font>
-    </x:dxf>
-  </x:dxfs>
-  <x:tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <x:colors>
-    <x:mruColors>
-      <x:color rgb="FF99CCFF"/>
-      <x:color rgb="FFC0C0C0"/>
-      <x:color rgb="FF666699"/>
-      <x:color rgb="FFFFFF99"/>
-    </x:mruColors>
-  </x:colors>
-  <x:extLst>
-    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
+  </numFmts>
+  <fonts count="5">
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color indexed="23"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="16">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFABABAB"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFABABAB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFABABAB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFABABAB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFABABAB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFABABAB"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFABABAB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFABABAB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFABABAB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFABABAB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFABABAB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFABABAB"/>
+      </right>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFABABAB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFABABAB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFABABAB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFABABAB"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFABABAB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFABABAB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFABABAB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFABABAB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFABABAB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFABABAB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFABABAB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFABABAB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFABABAB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFABABAB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="43">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" pivotButton="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" pivotButton="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="1" customBuiltin="0"/>
+  </cellStyles>
+  <dxfs count="13">
+    <dxf>
+      <font>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <i/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <i/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <i/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <i/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="48"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <i/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <i/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+      </font>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF99CCFF"/>
+      <color rgb="FFC0C0C0"/>
+      <color rgb="FF666699"/>
+      <color rgb="FFFFFF99"/>
+    </mruColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </x:ext>
-    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
       <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </x:ext>
-  </x:extLst>
-</x:styleSheet>
+    </ext>
+  </extLst>
+</styleSheet>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -676,10 +701,10 @@
     <dataField name="Sum Items total" fld="4" baseField="3" baseItem="0"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="1">
+    <format dxfId="0">
       <pivotArea grandRow="1" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="1">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" axis="axisRow" fieldPosition="0"/>
     </format>
     <format dxfId="2">
@@ -1195,7 +1220,7 @@
   </x:sortState>
   <x:phoneticPr fontId="0" type="noConversion"/>
   <x:conditionalFormatting sqref="C3:C6">
-    <x:cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="equal">
+    <x:cfRule type="cellIs" dxfId="8" priority="1" stopIfTrue="1" operator="equal">
       <x:formula>"VISA"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>

--- a/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/PivotSubtotalsSource/output.xlsx
+++ b/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/PivotSubtotalsSource/output.xlsx
@@ -82,7 +82,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <sz val="8"/>
       <name val="Arial"/>
@@ -102,19 +102,6 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -124,7 +111,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -147,182 +134,15 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFABABAB"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFABABAB"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFABABAB"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFABABAB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFABABAB"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFABABAB"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFABABAB"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFABABAB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFABABAB"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFABABAB"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFABABAB"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFABABAB"/>
-      </right>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFABABAB"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFABABAB"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFABABAB"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFABABAB"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFABABAB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFABABAB"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFABABAB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFABABAB"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFABABAB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFABABAB"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFABABAB"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFABABAB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFABABAB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFABABAB"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -353,72 +173,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" pivotButton="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" pivotButton="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1091,25 +845,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <x:c r="B2" s="3" t="s">
+      <x:c r="B2" s="2" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="s">
+      <x:c r="C2" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D2" s="4" t="s">
+      <x:c r="D2" s="3" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E2" s="4" t="s">
+      <x:c r="E2" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F2" s="3" t="s">
+      <x:c r="F2" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G2" s="4" t="s">
+      <x:c r="G2" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H2" s="4" t="s">
+      <x:c r="H2" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -1117,22 +871,22 @@
       <x:c r="B3" s="1" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C3" s="5" t="s">
+      <x:c r="C3" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D3" s="5" t="s">
+      <x:c r="D3" s="4" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E3" s="6">
+      <x:c r="E3" s="5">
         <x:v>32289</x:v>
       </x:c>
-      <x:c r="F3" s="7">
+      <x:c r="F3" s="6">
         <x:v>134.85</x:v>
       </x:c>
-      <x:c r="G3" s="8">
+      <x:c r="G3" s="7">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H3" s="7">
+      <x:c r="H3" s="6">
         <x:v>134.85</x:v>
       </x:c>
     </x:row>
@@ -1140,22 +894,22 @@
       <x:c r="B4" s="1" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C4" s="5" t="s">
+      <x:c r="C4" s="4" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D4" s="5" t="s">
+      <x:c r="D4" s="4" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E4" s="6">
+      <x:c r="E4" s="5">
         <x:v>32343</x:v>
       </x:c>
-      <x:c r="F4" s="7">
+      <x:c r="F4" s="6">
         <x:v>20108</x:v>
       </x:c>
-      <x:c r="G4" s="8">
+      <x:c r="G4" s="7">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H4" s="7">
+      <x:c r="H4" s="6">
         <x:v>20108</x:v>
       </x:c>
     </x:row>
@@ -1163,22 +917,22 @@
       <x:c r="B5" s="1" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="s">
+      <x:c r="C5" s="4" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D5" s="5" t="s">
+      <x:c r="D5" s="4" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E5" s="6">
+      <x:c r="E5" s="5">
         <x:v>32382</x:v>
       </x:c>
-      <x:c r="F5" s="7">
+      <x:c r="F5" s="6">
         <x:v>10152</x:v>
       </x:c>
-      <x:c r="G5" s="8">
+      <x:c r="G5" s="7">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H5" s="7">
+      <x:c r="H5" s="6">
         <x:v>10152</x:v>
       </x:c>
     </x:row>
@@ -1186,33 +940,33 @@
       <x:c r="B6" s="1" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="s">
+      <x:c r="C6" s="4" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D6" s="5" t="s">
+      <x:c r="D6" s="4" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="E6" s="6">
+      <x:c r="E6" s="5">
         <x:v>34261</x:v>
       </x:c>
-      <x:c r="F6" s="7">
+      <x:c r="F6" s="6">
         <x:v>1004.8</x:v>
       </x:c>
-      <x:c r="G6" s="8">
+      <x:c r="G6" s="7">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H6" s="7">
+      <x:c r="H6" s="6">
         <x:v>1004.8</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <x:c r="B7" s="9"/>
-      <x:c r="C7" s="9"/>
-      <x:c r="D7" s="9"/>
-      <x:c r="E7" s="10"/>
-      <x:c r="F7" s="11"/>
-      <x:c r="G7" s="12"/>
-      <x:c r="H7" s="11"/>
+      <x:c r="B7" s="8"/>
+      <x:c r="C7" s="8"/>
+      <x:c r="D7" s="8"/>
+      <x:c r="E7" s="9"/>
+      <x:c r="F7" s="10"/>
+      <x:c r="G7" s="11"/>
+      <x:c r="H7" s="10"/>
     </x:row>
   </x:sheetData>
   <x:sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:H207">
